--- a/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
+++ b/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="389">
   <si>
     <t>논리 ERD — Entity 6 · 관계 2</t>
   </si>
@@ -55,7 +55,10 @@
     <t>이력ID</t>
   </si>
   <si>
-    <t>휴무일 · 변경이력 은 관계선이 없다</t>
+    <t>휴무일 · 변경이력 · 운영기준 은 관계선이 없다</t>
+  </si>
+  <si>
+    <t>기준ID</t>
   </si>
   <si>
     <t>관계 (04)</t>
@@ -148,7 +151,16 @@
     <t>Write SP 8개가 남기는 컬럼 단위 변경기록</t>
   </si>
   <si>
-    <t>검사코드는 검사구성 문자열이 코드로 참조하므로 FK 관계선이 없다. 휴무일은 날짜로만 조회되는 독립 Master이고 변경이력도 Foreign Key를 갖지 않는다.</t>
+    <t>운영기준</t>
+  </si>
+  <si>
+    <t>운영시간 Master</t>
+  </si>
+  <si>
+    <t>운영시간과 마감시각 넷. 1행 고정이며 값의 소유자는 00 이다</t>
+  </si>
+  <si>
+    <t>검사코드는 검사구성 문자열이 코드로 참조하므로 FK 관계선이 없다. 휴무일은 날짜로만 조회되는 독립 Master이고 변경이력도 Foreign Key를 갖지 않는다. 운영기준도 그렇다 — 1행짜리 운영시간 Master이며 어느 업무 행과도 관계를 맺지 않는다.</t>
   </si>
   <si>
     <t>물리 ERD — Table 6 · Foreign Key 2</t>
@@ -433,6 +445,12 @@
     <t>성공한 데이터 변경의 컬럼 단위 기록</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>운영시간·마감시각 1행 고정. 값의 소유자는 00 이다</t>
+  </si>
+  <si>
     <t>컬럼 전건</t>
   </si>
   <si>
@@ -475,9 +493,6 @@
     <t>사용자 입력</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>정규화한 임의 테스트값</t>
   </si>
   <si>
@@ -679,6 +694,54 @@
     <t>NULL이면 값을 지운 상태</t>
   </si>
   <si>
+    <t>TINYINT</t>
+  </si>
+  <si>
+    <t>Seed 고정값 1</t>
+  </si>
+  <si>
+    <t>PK. 항상 1행이다</t>
+  </si>
+  <si>
+    <t>운영시작시각</t>
+  </si>
+  <si>
+    <t>TIME(0)</t>
+  </si>
+  <si>
+    <t>운영시간의 시작 (00 CP-04)</t>
+  </si>
+  <si>
+    <t>운영종료시각</t>
+  </si>
+  <si>
+    <t>운영시간의 끝. 이 시각부터 업무 불가 (00 CP-04)</t>
+  </si>
+  <si>
+    <t>일반예약AM마감</t>
+  </si>
+  <si>
+    <t>일반 당일예약의 오전 마감</t>
+  </si>
+  <si>
+    <t>일반예약PM마감</t>
+  </si>
+  <si>
+    <t>일반 당일예약의 오후 마감</t>
+  </si>
+  <si>
+    <t>접수AM마감</t>
+  </si>
+  <si>
+    <t>접수의 오전 마감. WalkIn 당일예약도 이 값을 쓴다</t>
+  </si>
+  <si>
+    <t>접수PM마감</t>
+  </si>
+  <si>
+    <t>접수의 오후 마감. WalkIn 당일예약도 이 값을 쓴다</t>
+  </si>
+  <si>
     <t>PK / FK / UQ / UX / CK / DF</t>
   </si>
   <si>
@@ -947,6 +1010,24 @@
   </si>
   <si>
     <t>기록일시 = SYSDATETIME()</t>
+  </si>
+  <si>
+    <t>PK_운영기준</t>
+  </si>
+  <si>
+    <t>기준ID Clustered</t>
+  </si>
+  <si>
+    <t>CK_운영기준_SINGLETON</t>
+  </si>
+  <si>
+    <t>기준ID = 1</t>
+  </si>
+  <si>
+    <t>CK_운영기준_HOURS</t>
+  </si>
+  <si>
+    <t>운영시작시각 &lt; 운영종료시각</t>
   </si>
   <si>
     <t>인덱스</t>
@@ -1780,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1961,172 +2042,202 @@
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="15" t="s">
+    <row r="26" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="16" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="16" t="s">
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="17" t="s">
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="C33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="D33" s="17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="17" t="s">
+      <c r="E33" s="17" t="s">
         <v>22</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="17" t="s">
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="C43" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="18" t="s">
+      <c r="E43" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
@@ -2142,7 +2253,9 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="J22:K22"/>
     <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="B46:K46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2174,12 +2287,12 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2233,10 +2346,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>2</v>
@@ -2245,10 +2358,10 @@
         <v>6</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L6" s="19" t="s">
         <v>2</v>
@@ -2257,357 +2370,357 @@
         <v>9</v>
       </c>
       <c r="N6" s="21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O6" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="23"/>
       <c r="C7" s="24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="23"/>
       <c r="H7" s="24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L7" s="23"/>
       <c r="M7" s="24" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N7" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="23"/>
       <c r="C8" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>50</v>
-      </c>
       <c r="E8" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="23"/>
       <c r="H8" s="24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L8" s="23"/>
       <c r="M8" s="24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N8" s="24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="23"/>
       <c r="C9" s="24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L9" s="23"/>
       <c r="M9" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="25" t="s">
         <v>60</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="25" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="19" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H10" s="20" t="s">
         <v>3</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J10" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L10" s="23"/>
       <c r="M10" s="24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N10" s="24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11" s="23"/>
       <c r="C11" s="24" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="23"/>
       <c r="H11" s="24" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N11" s="29" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O11" s="30" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="19" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G12" s="23"/>
       <c r="H12" s="24" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="23"/>
       <c r="C13" s="24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="24" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="23"/>
       <c r="C14" s="24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G14" s="23"/>
       <c r="H14" s="24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="23"/>
       <c r="C15" s="24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="23"/>
       <c r="C16" s="24" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="23"/>
       <c r="C20" s="24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="23"/>
       <c r="C21" s="24" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="28"/>
       <c r="C22" s="30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.25">
@@ -2643,16 +2756,16 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G26" s="19" t="s">
         <v>2</v>
@@ -2661,10 +2774,10 @@
         <v>10</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J26" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L26" s="19" t="s">
         <v>2</v>
@@ -2673,10 +2786,10 @@
         <v>11</v>
       </c>
       <c r="N26" s="21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O26" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
@@ -2684,198 +2797,198 @@
         <v>2</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="24" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L27" s="23"/>
       <c r="M27" s="24" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="N27" s="24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="23"/>
       <c r="C28" s="24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L28" s="23"/>
       <c r="M28" s="24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N28" s="24" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O28" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="28"/>
       <c r="C29" s="29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G29" s="23"/>
       <c r="H29" s="24" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L29" s="23"/>
       <c r="M29" s="24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N29" s="24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G30" s="23"/>
       <c r="H30" s="24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L30" s="23"/>
       <c r="M30" s="24" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N30" s="24" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O30" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G31" s="23"/>
       <c r="H31" s="24" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L31" s="23"/>
       <c r="M31" s="24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="N31" s="24" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O31" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G32" s="23"/>
       <c r="H32" s="24" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L32" s="23"/>
       <c r="M32" s="24" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N32" s="24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O32" s="25" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="28"/>
       <c r="H33" s="29" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J33" s="30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L33" s="28"/>
       <c r="M33" s="29" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O33" s="30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
@@ -2889,10 +3002,10 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
@@ -2906,10 +3019,10 @@
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -2923,49 +3036,49 @@
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D44" s="17" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +3108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3007,24 +3120,24 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -3032,101 +3145,118 @@
         <v>4</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="34" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="34" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>137</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3138,7 +3268,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3152,35 +3282,35 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>4</v>
@@ -3189,389 +3319,389 @@
         <v>3</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C5" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>50</v>
-      </c>
       <c r="E5" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>4</v>
@@ -3580,228 +3710,228 @@
         <v>6</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G20" s="36" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E21" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G21" s="36" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G23" s="36" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G26" s="36" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G27" s="36" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>4</v>
@@ -3810,136 +3940,136 @@
         <v>9</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C33" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="34" t="s">
-        <v>56</v>
-      </c>
       <c r="F33" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="35" t="s">
         <v>4</v>
@@ -3948,182 +4078,182 @@
         <v>10</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D38" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G41" s="36" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F42" s="36" t="s">
         <v>4</v>
       </c>
       <c r="G42" s="36" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C43" s="36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G43" s="36" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44" s="33" t="s">
         <v>4</v>
@@ -4132,90 +4262,90 @@
         <v>3</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E44" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F44" s="34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E45" s="34" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F45" s="34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F46" s="34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F47" s="34" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="35" t="s">
         <v>4</v>
@@ -4224,177 +4354,338 @@
         <v>11</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G48" s="36" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G49" s="36" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" s="35" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G50" s="36" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="35" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C51" s="36" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G51" s="36" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" s="35" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C52" s="36" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G52" s="36" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C53" s="36" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G53" s="36" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" s="35" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C54" s="36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G54" s="36" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="35" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C55" s="36" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G55" s="36" t="s">
-        <v>219</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G57" s="34" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G58" s="34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G59" s="34" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="G62" s="34" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -4406,7 +4697,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4417,679 +4708,721 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>59</v>
-      </c>
       <c r="D17" s="36" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="D24" s="36" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C27" s="34" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="35" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="D41" s="36" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B43" s="33" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="D45" s="34" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="35" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="D46" s="36" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="D47" s="36" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="D48" s="36" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="D49" s="36" t="s">
-        <v>309</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -5113,158 +5446,158 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5286,150 +5619,150 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>336</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>344</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>

--- a/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
+++ b/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="389">
   <si>
-    <t>논리 ERD — Entity 6 · 관계 2</t>
+    <t>논리 ERD — Entity 7 · 관계 2</t>
   </si>
   <si>
     <t>실선 = Foreign Key 2개  ·  점선 = FK 가 아닌 코드 문자열 참조</t>
@@ -163,7 +163,7 @@
     <t>검사코드는 검사구성 문자열이 코드로 참조하므로 FK 관계선이 없다. 휴무일은 날짜로만 조회되는 독립 Master이고 변경이력도 Foreign Key를 갖지 않는다. 운영기준도 그렇다 — 1행짜리 운영시간 Master이며 어느 업무 행과도 관계를 맺지 않는다.</t>
   </si>
   <si>
-    <t>물리 ERD — Table 6 · Foreign Key 2</t>
+    <t>물리 ERD — Table 7 · Foreign Key 2</t>
   </si>
   <si>
     <t>실선 = Foreign Key  ·  NULL 열:  X = NOT NULL   O = NULL 허용</t>
@@ -397,7 +397,7 @@
     <t>FK_완료이력_수검자</t>
   </si>
   <si>
-    <t>물리 테이블 6개</t>
+    <t>물리 테이블 7개</t>
   </si>
   <si>
     <t>No</t>

--- a/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
+++ b/docs/baseline/output/04_검진_예약접수_DB설계서.xlsx
@@ -1042,7 +1042,7 @@
     <t>목적</t>
   </si>
   <si>
-    <t>차트번호 정확조회·고유성</t>
+    <t>차트번호 고유성. 조회는 포함검색이라 이 Index 를 타지 않는다</t>
   </si>
   <si>
     <t>주민번호 테스트값 정확조회·고유성</t>
@@ -1057,7 +1057,7 @@
     <t>수검자ID, 차트번호, 성별, 휴대전화</t>
   </si>
   <si>
-    <t>이름 조회·이름+생년월일 중복후보</t>
+    <t>이름+생년월일 중복후보. 이름 조회는 포함검색이라 이 Index 를 타지 않는다</t>
   </si>
   <si>
     <t>IX_수검자_BIRTHDAY</t>
